--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3574,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121277546</v>
+        <v>121277547</v>
       </c>
       <c r="B26" t="n">
-        <v>97975</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487408</v>
+        <v>487443</v>
       </c>
       <c r="R26" t="n">
         <v>6963363</v>
@@ -3662,7 +3662,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3680,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121277547</v>
+        <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>57348</v>
+        <v>97985</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3693,31 +3692,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3725,7 +3724,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487443</v>
+        <v>487408</v>
       </c>
       <c r="R27" t="n">
         <v>6963363</v>
@@ -3769,6 +3768,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3683,7 +3683,7 @@
         <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>97985</v>
+        <v>97998</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3574,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121277547</v>
+        <v>121277546</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>97999</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487443</v>
+        <v>487408</v>
       </c>
       <c r="R26" t="n">
         <v>6963363</v>
@@ -3662,6 +3662,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3680,10 +3681,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121277546</v>
+        <v>121277547</v>
       </c>
       <c r="B27" t="n">
-        <v>97998</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3692,31 +3693,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3724,7 +3725,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487408</v>
+        <v>487443</v>
       </c>
       <c r="R27" t="n">
         <v>6963363</v>
@@ -3768,7 +3769,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3577,7 +3577,7 @@
         <v>121277546</v>
       </c>
       <c r="B26" t="n">
-        <v>97999</v>
+        <v>98002</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>121277547</v>
       </c>
       <c r="B27" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3574,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121277546</v>
+        <v>121277547</v>
       </c>
       <c r="B26" t="n">
-        <v>98002</v>
+        <v>57355</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487408</v>
+        <v>487443</v>
       </c>
       <c r="R26" t="n">
         <v>6963363</v>
@@ -3662,7 +3662,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3680,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121277547</v>
+        <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>57354</v>
+        <v>98008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3693,31 +3692,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3725,7 +3724,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487443</v>
+        <v>487408</v>
       </c>
       <c r="R27" t="n">
         <v>6963363</v>
@@ -3769,6 +3768,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3577,7 +3577,7 @@
         <v>121277547</v>
       </c>
       <c r="B26" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>98008</v>
+        <v>98009</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3574,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121277547</v>
+        <v>121277546</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>98009</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487443</v>
+        <v>487408</v>
       </c>
       <c r="R26" t="n">
         <v>6963363</v>
@@ -3662,6 +3662,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3680,10 +3681,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121277546</v>
+        <v>121277547</v>
       </c>
       <c r="B27" t="n">
-        <v>98009</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3692,31 +3693,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3724,7 +3725,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487408</v>
+        <v>487443</v>
       </c>
       <c r="R27" t="n">
         <v>6963363</v>
@@ -3768,7 +3769,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3574,10 +3574,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121277546</v>
+        <v>121277547</v>
       </c>
       <c r="B26" t="n">
-        <v>98009</v>
+        <v>57356</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3586,31 +3586,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>487408</v>
+        <v>487443</v>
       </c>
       <c r="R26" t="n">
         <v>6963363</v>
@@ -3662,7 +3662,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3681,10 +3680,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121277547</v>
+        <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>98009</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3693,31 +3692,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3725,7 +3724,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>487443</v>
+        <v>487408</v>
       </c>
       <c r="R27" t="n">
         <v>6963363</v>
@@ -3769,6 +3768,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52254-2019 artfynd.xlsx
+++ b/artfynd/A 52254-2019 artfynd.xlsx
@@ -3577,7 +3577,7 @@
         <v>121277547</v>
       </c>
       <c r="B26" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>121277546</v>
       </c>
       <c r="B27" t="n">
-        <v>98009</v>
+        <v>98014</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
